--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T20:30:38+00:00</t>
+    <t>2026-05-03T21:28:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-03T21:28:00+00:00</t>
+    <t>2026-05-04T06:23:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:23:23+00:00</t>
+    <t>2026-05-04T06:44:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T06:44:52+00:00</t>
+    <t>2026-05-04T07:06:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:06:34+00:00</t>
+    <t>2026-05-04T07:30:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:30:32+00:00</t>
+    <t>2026-05-04T07:50:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T07:50:36+00:00</t>
+    <t>2026-05-04T08:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:11:13+00:00</t>
+    <t>2026-05-04T08:32:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T08:32:13+00:00</t>
+    <t>2026-05-04T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:30:07+00:00</t>
+    <t>2026-05-04T09:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T09:51:52+00:00</t>
+    <t>2026-05-04T11:25:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:25:12+00:00</t>
+    <t>2026-05-04T11:47:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T11:47:21+00:00</t>
+    <t>2026-05-04T12:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$22</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="219">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T12:11:06+00:00</t>
+    <t>2026-05-04T13:22:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -493,25 +493,6 @@
   </si>
   <si>
     <t>OncoBox 2.0 K03: Wurde ein Screening zur Studienteilnahme durchgeführt? Mapping auf Stud_Screening (0=nein, 1=ja)</t>
-  </si>
-  <si>
-    <t>ResearchSubject.extension:StudiennameCode</t>
-  </si>
-  <si>
-    <t>StudiennameCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://www.senologie.org/fhir/StructureDefinition/ex-senologie-studienname-code}
-</t>
-  </si>
-  <si>
-    <t>Studienname aus Auswahlliste (K02)</t>
-  </si>
-  <si>
-    <t>OncoBox 2.0 K02: Kodierter Studienname aus Auswahlliste. Ergänzt die study-Referenz um einen strukturierten Code für die OncoBox-Meldung.</t>
-  </si>
-  <si>
-    <t>OncoBox 2.0 K02: Kodierter Studienname aus Auswahlliste. Ergänzt study.display um einen strukturierten Code.</t>
   </si>
   <si>
     <t>ResearchSubject.extension:Kontakt</t>
@@ -1037,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN23"/>
+  <dimension ref="A1:AN22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.265625" customWidth="true" bestFit="true"/>
@@ -2496,7 +2477,7 @@
         <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2575,46 +2556,46 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="C14" s="2"/>
+      <c r="D14" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="C14" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>20</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="N14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>20</v>
       </c>
@@ -2662,7 +2643,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>139</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -2671,7 +2652,7 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>140</v>
@@ -2683,7 +2664,7 @@
         <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>20</v>
@@ -2691,14 +2672,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>171</v>
+        <v>20</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2711,26 +2692,22 @@
         <v>20</v>
       </c>
       <c r="I15" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J15" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="J15" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K15" t="s" s="2">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N15" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="O15" t="s" s="2">
-        <v>175</v>
-      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>20</v>
       </c>
@@ -2778,7 +2755,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -2790,27 +2767,27 @@
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>20</v>
+        <v>175</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" hidden="true">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2818,22 +2795,22 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J16" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>178</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>179</v>
@@ -2841,7 +2818,9 @@
       <c r="M16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="N16" s="2"/>
+      <c r="N16" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -2866,13 +2845,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>20</v>
+        <v>183</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>20</v>
+        <v>184</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -2890,13 +2869,13 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
@@ -2905,32 +2884,32 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>89</v>
@@ -2939,23 +2918,21 @@
         <v>90</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>109</v>
+        <v>190</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -2980,34 +2957,34 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="Y17" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>184</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>89</v>
@@ -3019,32 +2996,32 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
@@ -3067,7 +3044,9 @@
       <c r="M18" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="N18" s="2"/>
+      <c r="N18" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3116,10 +3095,10 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>89</v>
@@ -3131,7 +3110,7 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>20</v>
@@ -3140,7 +3119,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -3179,9 +3158,7 @@
       <c r="M19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="N19" t="s" s="2">
-        <v>205</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3245,7 +3222,7 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>206</v>
+        <v>85</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
@@ -3259,10 +3236,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3270,7 +3247,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -3282,18 +3259,20 @@
         <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -3342,10 +3321,10 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>89</v>
@@ -3357,7 +3336,7 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
@@ -3369,7 +3348,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>211</v>
       </c>
@@ -3388,7 +3367,7 @@
         <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>20</v>
@@ -3397,17 +3376,15 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>215</v>
-      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -3471,7 +3448,7 @@
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
@@ -3483,12 +3460,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3502,7 +3479,7 @@
         <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
@@ -3511,13 +3488,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3568,7 +3545,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3583,7 +3560,7 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
@@ -3595,120 +3572,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="C23" s="2"/>
-      <c r="D23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G23" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H23" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K23" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q23" s="2"/>
-      <c r="R23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AN23">
+  <autoFilter ref="A1:AN22">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -3718,7 +3583,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI22">
+  <conditionalFormatting sqref="A2:AI21">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:22:07+00:00</t>
+    <t>2026-05-04T13:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T13:47:49+00:00</t>
+    <t>2026-05-04T14:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:15:24+00:00</t>
+    <t>2026-05-04T14:55:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:55:41+00:00</t>
+    <t>2026-05-04T15:18:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T15:18:17+00:00</t>
+    <t>2026-05-04T15:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T18:43:40+00:00</t>
+    <t>2026-05-12T08:39:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
+++ b/ci-build/StructureDefinition-senologie-studienteilnahme.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$22</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="221">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T08:39:42+00:00</t>
+    <t>2026-05-12T14:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -235,6 +235,12 @@
   </si>
   <si>
     <t>Constraint(s)</t>
+  </si>
+  <si>
+    <t>Mapping: BIH LM Senologie</t>
+  </si>
+  <si>
+    <t>Mapping: LM-Element: Studienteilnahme</t>
   </si>
   <si>
     <t>Mapping: BRIDG 5.1 Mapping</t>
@@ -1018,7 +1024,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN22"/>
+  <dimension ref="A1:AP22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.265625" customWidth="true" bestFit="true"/>
@@ -1056,10 +1062,12 @@
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="150.1328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.1328125" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="41.046875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.35546875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="37.24609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="150.1328125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="41.046875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1183,6 +1191,12 @@
       <c r="AN1" t="s" s="1">
         <v>76</v>
       </c>
+      <c r="AO1" t="s" s="1">
+        <v>77</v>
+      </c>
+      <c r="AP1" t="s" s="1">
+        <v>78</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1193,14 +1207,14 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1212,16 +1226,16 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -1274,36 +1288,42 @@
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>87</v>
       </c>
       <c r="AN2" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AO2" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AP2" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1311,10 +1331,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1323,19 +1343,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1385,13 +1405,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1409,15 +1429,21 @@
         <v>20</v>
       </c>
       <c r="AN3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP3" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1425,10 +1451,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1437,16 +1463,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1497,19 +1523,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1521,15 +1547,21 @@
         <v>20</v>
       </c>
       <c r="AN4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO4" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP4" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1537,31 +1569,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1611,19 +1643,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1635,15 +1667,21 @@
         <v>20</v>
       </c>
       <c r="AN5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO5" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP5" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1651,10 +1689,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1666,16 +1704,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1701,13 +1739,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -1725,19 +1763,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -1749,26 +1787,32 @@
         <v>20</v>
       </c>
       <c r="AN6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO6" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP6" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1780,16 +1824,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1839,19 +1883,19 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
@@ -1860,29 +1904,35 @@
         <v>20</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="AN7" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -1894,16 +1944,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1953,13 +2003,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -1974,18 +2024,24 @@
         <v>20</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN8" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1993,10 +2049,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2008,13 +2064,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2053,29 +2109,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2087,28 +2143,34 @@
         <v>20</v>
       </c>
       <c r="AN9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP9" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
@@ -2120,16 +2182,16 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2179,19 +2241,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2203,28 +2265,34 @@
         <v>20</v>
       </c>
       <c r="AN10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP10" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -2236,16 +2304,16 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2295,19 +2363,19 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
@@ -2319,28 +2387,34 @@
         <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP11" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2352,16 +2426,16 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2411,19 +2485,19 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -2435,28 +2509,34 @@
         <v>20</v>
       </c>
       <c r="AN12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP12" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2468,16 +2548,16 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2527,19 +2607,19 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
@@ -2551,50 +2631,56 @@
         <v>20</v>
       </c>
       <c r="AN13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -2643,19 +2729,19 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
@@ -2664,18 +2750,24 @@
         <v>20</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="AN14" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2683,10 +2775,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -2695,16 +2787,16 @@
         <v>20</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2755,39 +2847,45 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>177</v>
+        <v>20</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AP15" t="s" s="2">
+        <v>179</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2795,31 +2893,31 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2845,13 +2943,13 @@
         <v>20</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>20</v>
@@ -2869,68 +2967,74 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>187</v>
+        <v>20</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AP16" t="s" s="2">
+        <v>189</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2981,39 +3085,45 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>193</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>194</v>
+        <v>20</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP17" t="s" s="2">
+        <v>196</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3021,31 +3131,31 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3095,39 +3205,45 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>20</v>
+        <v>202</v>
       </c>
       <c r="AN18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3135,28 +3251,28 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3207,39 +3323,45 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="AN19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP19" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3247,13 +3369,13 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>20</v>
@@ -3262,16 +3384,16 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3321,39 +3443,45 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="AN20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3361,10 +3489,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -3376,13 +3504,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3433,39 +3561,45 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>20</v>
+        <v>212</v>
       </c>
       <c r="AN21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3473,13 +3607,13 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
@@ -3488,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3545,35 +3679,41 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>218</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
       </c>
+      <c r="AO22" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP22" t="s" s="2">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN22">
+  <autoFilter ref="A1:AP22">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
